--- a/Python Programs/GameDesignPlanner/questions.xlsx
+++ b/Python Programs/GameDesignPlanner/questions.xlsx
@@ -1,34 +1,255 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python Programs\GameDesignPlanner\dist\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5D005D-D033-4D96-8B6A-ECEFA6456B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="12735" yWindow="780" windowWidth="25140" windowHeight="18720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="기본" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="샘플" sheetId="11" r:id="rId1"/>
+    <sheet name="디자인 필라" sheetId="6" r:id="rId2"/>
+    <sheet name="컨셉 기획" sheetId="2" r:id="rId3"/>
+    <sheet name="세부 기획" sheetId="3" r:id="rId4"/>
+    <sheet name="기획 회고" sheetId="10" r:id="rId5"/>
+    <sheet name="개발 계획" sheetId="9" r:id="rId6"/>
+    <sheet name="테스트 설계" sheetId="4" r:id="rId7"/>
+    <sheet name="테스트 회고" sheetId="8" r:id="rId8"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="52">
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>컨셉</t>
+  </si>
+  <si>
+    <t>이 게임의 핵심 판타지는 무엇인가</t>
+  </si>
+  <si>
+    <t>플레이어는 어떤 역할을 수행하는가</t>
+  </si>
+  <si>
+    <t>시스템</t>
+  </si>
+  <si>
+    <t>주요 성장 루프는 무엇인가</t>
+  </si>
+  <si>
+    <t>반복 플레이의 동기는 무엇인가</t>
+  </si>
+  <si>
+    <t>정성적 평가 방안</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정량적 평가 방안</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평가 항목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 (ex: 말초적인 액션 재미 검증)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>핵심 경험은 무엇인가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컨셉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시스템/컨텐츠 목적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레퍼런스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설계</t>
+  </si>
+  <si>
+    <t>설계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개요</t>
+  </si>
+  <si>
+    <t>개요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수준 (프로토타입, 프로덕션, …)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달성 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋았던 점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나빴던 점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개선 방안 (효율화, … )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예상되는 문제 (ex: 몬스터 AI)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해결 방안 (ex: 수치 튜닝 방안)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요 과제 (주안점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하고자 하는 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목표 형태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목표 달성 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>집중 연구 필요한 항목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업 분량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가용 자원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제반사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해야 할 일 목록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 개발 단계 (프로토타입, 기획, 개선, 개발)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목표 개발 수준 (프로토타입, 프로덕션, …)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달성하고자 하는 목표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업 일정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +268,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,75 +570,503 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC46AA8-3F20-4EE7-8C42-BB763C321A46}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="33.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>컨셉</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>이 게임의 핵심 판타지는 무엇인가</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>컨셉</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>플레이어는 어떤 역할을 수행하는가</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>시스템</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>주요 성장 루프는 무엇인가</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>시스템</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>반복 플레이의 동기는 무엇인가</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A674DE91-E7A4-4EA5-B51C-30782373A803}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="20.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52AFAB43-8090-40F9-B687-F972834FA52D}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E4EE3B-D083-4055-BCB9-69CA2F620B5E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6D8955-CE61-41A5-A0B2-A3422F042B37}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="28.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7973EA-66DA-4A50-8BA3-063A33557865}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376510F4-42A3-405D-889E-6FDF6886D888}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="32.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C4ED04-052C-4028-8CD0-90EEF1608CF2}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>